--- a/assets/business/valuation/Valuation Template.xlsx
+++ b/assets/business/valuation/Valuation Template.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brishabh/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079ECE48-75E2-B845-A929-EA412952CF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB226C2-6CC2-4C41-9856-6B59DEA3FADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21700" yWindow="-23560" windowWidth="30240" windowHeight="17000" xr2:uid="{CD73A073-6F59-C94D-8268-42A325A7E6A8}"/>
+    <workbookView xWindow="11240" yWindow="-24820" windowWidth="34200" windowHeight="20060" activeTab="1" xr2:uid="{CD73A073-6F59-C94D-8268-42A325A7E6A8}"/>
   </bookViews>
   <sheets>
     <sheet name="BRK" sheetId="1" r:id="rId1"/>
-    <sheet name="DCF Template" sheetId="2" r:id="rId2"/>
-    <sheet name="Invert" sheetId="3" r:id="rId3"/>
+    <sheet name="FISV" sheetId="4" r:id="rId2"/>
+    <sheet name="DCF Template" sheetId="2" r:id="rId3"/>
+    <sheet name="Invert" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029" iterate="1" iterateDelta="9.9999999999994451E-4"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="9.9999999999994451E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="63">
   <si>
     <t>Terminal 
 Value</t>
@@ -245,6 +246,12 @@
   <si>
     <t>Formula: NYU - Prof Aswath Damodran</t>
   </si>
+  <si>
+    <t>FISV</t>
+  </si>
+  <si>
+    <t>Market cap (millions)</t>
+  </si>
 </sst>
 </file>
 
@@ -252,7 +259,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -744,7 +751,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -812,23 +819,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -837,7 +842,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -853,8 +858,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -862,7 +867,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="11" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -872,14 +877,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -887,27 +886,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF00B050"/>
@@ -1004,6 +983,55 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA645ACD-C52C-2444-ACB2-01893AAAD090}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5156200" y="9690100"/>
+          <a:ext cx="4546600" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>9</xdr:row>
@@ -1047,10 +1075,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1380,7 +1404,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="17" thickBot="1"/>
     <row r="2" spans="1:16" ht="17" thickBot="1">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="47" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="1"/>
@@ -1400,32 +1424,21 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="7"/>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="42">
+      <c r="C3" s="41">
         <v>1060</v>
       </c>
       <c r="D3" s="39"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
       <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="7"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="42">
         <v>485.39</v>
       </c>
       <c r="D4" s="6"/>
@@ -1434,10 +1447,10 @@
     </row>
     <row r="5" spans="1:16" ht="17" customHeight="1" thickBot="1">
       <c r="A5" s="7"/>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="49">
+      <c r="C5" s="48">
         <v>0</v>
       </c>
       <c r="D5" s="30"/>
@@ -1451,13 +1464,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="7"/>
-      <c r="B6" s="40" t="s">
+      <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="40">
         <v>2025</v>
       </c>
       <c r="E6" s="12">
@@ -1571,43 +1584,43 @@
         <v>PV(10%)</v>
       </c>
       <c r="D8" s="14">
-        <f>D7*(1+$O$8)^($D$6-D6-1)*$C$5</f>
+        <f t="shared" ref="D8:M8" si="1">D7*(1+$O$8)^($D$6-D6-1)*$C$5</f>
         <v>0</v>
       </c>
       <c r="E8" s="14">
-        <f>E7*(1+$O$8)^($D$6-E6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F8" s="14">
-        <f>F7*(1+$O$8)^($D$6-F6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G8" s="14">
-        <f>G7*(1+$O$8)^($D$6-G6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H8" s="14">
-        <f>H7*(1+$O$8)^($D$6-H6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f>I7*(1+$O$8)^($D$6-I6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="14">
-        <f>J7*(1+$O$8)^($D$6-J6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K8" s="14">
-        <f>K7*(1+$O$8)^($D$6-K6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L8" s="14">
-        <f>L7*(1+$O$8)^($D$6-L6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M8" s="14">
-        <f>M7*(1+$O$8)^($D$6-M6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N8" s="14">
@@ -1674,39 +1687,39 @@
         <v>2025</v>
       </c>
       <c r="E12" s="12">
-        <f t="shared" ref="E12:M12" si="1">D12+1</f>
+        <f t="shared" ref="E12:M12" si="2">D12+1</f>
         <v>2026</v>
       </c>
       <c r="F12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2027</v>
       </c>
       <c r="G12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2028</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2029</v>
       </c>
       <c r="I12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2030</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2031</v>
       </c>
       <c r="K12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2032</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2033</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2034</v>
       </c>
       <c r="N12" s="12">
@@ -1788,43 +1801,43 @@
         <v>PV(10%)</v>
       </c>
       <c r="D14" s="14">
-        <f>D13*(1+$O$14)^($D$12-D12-1)*$C$5</f>
+        <f t="shared" ref="D14:M14" si="3">D13*(1+$O$14)^($D$12-D12-1)*$C$5</f>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f>E13*(1+$O$14)^($D$12-E12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f>F13*(1+$O$14)^($D$12-F12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f>G13*(1+$O$14)^($D$12-G12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f>H13*(1+$O$14)^($D$12-H12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f>I13*(1+$O$14)^($D$12-I12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f>J13*(1+$O$14)^($D$12-J12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f>K13*(1+$O$14)^($D$12-K12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L14" s="14">
-        <f>L13*(1+$O$14)^($D$12-L12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M14" s="14">
-        <f>M13*(1+$O$14)^($D$12-M12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14" s="14">
@@ -1892,39 +1905,39 @@
         <v>2025</v>
       </c>
       <c r="E18" s="12">
-        <f t="shared" ref="E18:M18" si="2">D18+1</f>
+        <f t="shared" ref="E18:M18" si="4">D18+1</f>
         <v>2026</v>
       </c>
       <c r="F18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2027</v>
       </c>
       <c r="G18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2028</v>
       </c>
       <c r="H18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2029</v>
       </c>
       <c r="I18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2030</v>
       </c>
       <c r="J18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2031</v>
       </c>
       <c r="K18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2032</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2033</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2034</v>
       </c>
       <c r="N18" s="12">
@@ -2006,47 +2019,47 @@
         <v>PV(10%)</v>
       </c>
       <c r="D20" s="14">
-        <f>D19*(1+$O$20)^($D$18-D18-1)*$C$5</f>
+        <f t="shared" ref="D20:M20" si="5">D19*(1+$O$20)^($D$18-D18-1)*$C$5</f>
         <v>0</v>
       </c>
       <c r="E20" s="14">
-        <f>E19*(1+$O$20)^($D$18-E18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <f>F19*(1+$O$20)^($D$18-F18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G20" s="14">
-        <f>G19*(1+$O$20)^($D$18-G18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H20" s="14">
-        <f>H19*(1+$O$20)^($D$18-H18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f>I19*(1+$O$20)^($D$18-I18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J20" s="14">
-        <f>J19*(1+$O$20)^($D$18-J18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K20" s="14">
-        <f>K19*(1+$O$20)^($D$18-K18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L20" s="14">
-        <f>L19*(1+$O$20)^($D$18-L18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M20" s="14">
-        <f>M19*(1+$O$20)^($D$18-M18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N20" s="14">
-        <f t="shared" ref="N20" si="3">N19*(1+$O$20)^($D$18-N18-1)</f>
+        <f t="shared" ref="N20" si="6">N19*(1+$O$20)^($D$18-N18-1)</f>
         <v>337.33075942248701</v>
       </c>
       <c r="O20" s="13">
@@ -2153,7 +2166,7 @@
       <c r="C26" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="50">
         <v>0.33</v>
       </c>
       <c r="E26" s="25">
@@ -2217,15 +2230,15 @@
     </row>
     <row r="36" spans="2:11" ht="17" thickBot="1"/>
     <row r="37" spans="2:11" ht="17" thickBot="1">
-      <c r="B37" s="72"/>
-      <c r="C37" s="73"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="71"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="74" t="s">
+      <c r="G37" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="75" t="s">
+      <c r="H37" s="73" t="s">
         <v>38</v>
       </c>
       <c r="I37" s="3"/>
@@ -2233,300 +2246,212 @@
       <c r="K37" s="4"/>
     </row>
     <row r="38" spans="2:11" ht="17" thickBot="1">
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="56">
+      <c r="C38" s="54">
         <v>1047150</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="57" t="s">
+      <c r="G38" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="H38" s="58">
+      <c r="H38" s="56">
         <v>0.12</v>
       </c>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
       <c r="K38" s="7"/>
     </row>
     <row r="39" spans="2:11">
-      <c r="B39" s="76"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="57" t="s">
+      <c r="B39" s="74"/>
+      <c r="C39" s="51"/>
+      <c r="G39" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="H39" s="58">
+      <c r="H39" s="56">
         <v>0.09</v>
       </c>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
       <c r="K39" s="7"/>
     </row>
     <row r="40" spans="2:11">
-      <c r="B40" s="78" t="s">
+      <c r="B40" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="57" t="s">
+      <c r="C40" s="51"/>
+      <c r="G40" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="H40" s="58">
+      <c r="H40" s="56">
         <v>0.08</v>
       </c>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
       <c r="K40" s="7"/>
     </row>
     <row r="41" spans="2:11">
-      <c r="B41" s="76" t="s">
+      <c r="B41" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="C41" s="60" t="s">
+      <c r="C41" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="57" t="s">
+      <c r="G41" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H41" s="58">
+      <c r="H41" s="56">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
       <c r="K41" s="7"/>
     </row>
     <row r="42" spans="2:11">
-      <c r="B42" s="79" t="s">
+      <c r="B42" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="61">
+      <c r="C42" s="59">
         <f>VLOOKUP(C41,G38:H43,2)</f>
         <v>0.08</v>
       </c>
-      <c r="D42" s="80"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
-      <c r="G42" s="57" t="s">
+      <c r="D42" s="60"/>
+      <c r="G42" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="H42" s="58">
+      <c r="H42" s="56">
         <v>0.06</v>
       </c>
-      <c r="I42" s="40"/>
-      <c r="J42" s="40"/>
       <c r="K42" s="7"/>
     </row>
     <row r="43" spans="2:11">
-      <c r="B43" s="79" t="s">
+      <c r="B43" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="63">
+      <c r="C43" s="61">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="57" t="s">
+      <c r="G43" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="H43" s="64">
+      <c r="H43" s="62">
         <v>0.1</v>
       </c>
-      <c r="I43" s="40"/>
-      <c r="J43" s="40"/>
       <c r="K43" s="7"/>
     </row>
     <row r="44" spans="2:11">
-      <c r="B44" s="79" t="s">
+      <c r="B44" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="63">
+      <c r="C44" s="61">
         <v>0.04</v>
       </c>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="40"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="63"/>
       <c r="K44" s="7"/>
     </row>
     <row r="45" spans="2:11">
-      <c r="B45" s="76"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="40"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="81"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="40"/>
+      <c r="B45" s="74"/>
+      <c r="C45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="63"/>
       <c r="K45" s="7"/>
     </row>
     <row r="46" spans="2:11">
-      <c r="B46" s="78" t="s">
+      <c r="B46" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="77"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="40"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="77"/>
-      <c r="H46" s="81"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="40"/>
+      <c r="C46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="63"/>
       <c r="K46" s="7"/>
     </row>
     <row r="47" spans="2:11">
-      <c r="B47" s="79" t="s">
+      <c r="B47" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="63">
+      <c r="C47" s="61">
         <v>0.182</v>
       </c>
-      <c r="D47" s="40"/>
-      <c r="E47" s="40"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="81"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="40"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="63"/>
       <c r="K47" s="7"/>
     </row>
     <row r="48" spans="2:11">
-      <c r="B48" s="79" t="s">
+      <c r="B48" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="63">
+      <c r="C48" s="61">
         <v>0.1104</v>
       </c>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="81"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="40"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="63"/>
       <c r="K48" s="7"/>
     </row>
     <row r="49" spans="2:11" ht="17" thickBot="1">
-      <c r="B49" s="76"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="77"/>
-      <c r="H49" s="81"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="51"/>
+      <c r="G49" s="51"/>
+      <c r="H49" s="63"/>
       <c r="K49" s="7"/>
     </row>
     <row r="50" spans="2:11" ht="17" thickBot="1">
-      <c r="B50" s="76" t="s">
+      <c r="B50" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="66">
+      <c r="C50" s="64">
         <f>C38/(C47*(1+C44)*(1-C44/C48)/(C42-C44))</f>
         <v>347024.85014985013</v>
       </c>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="63"/>
       <c r="K50" s="7"/>
     </row>
     <row r="51" spans="2:11">
-      <c r="B51" s="76"/>
-      <c r="C51" s="82"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="77"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="65"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="63"/>
       <c r="K51" s="7"/>
     </row>
     <row r="52" spans="2:11">
-      <c r="B52" s="76" t="s">
+      <c r="B52" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="82"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="77"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="40"/>
+      <c r="C52" s="65"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="63"/>
       <c r="K52" s="7"/>
     </row>
     <row r="53" spans="2:11">
-      <c r="B53" s="79" t="s">
+      <c r="B53" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="68">
+      <c r="C53" s="66">
         <v>5</v>
       </c>
-      <c r="D53" s="40"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="77"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="40"/>
+      <c r="G53" s="51"/>
+      <c r="H53" s="63"/>
       <c r="K53" s="7"/>
     </row>
     <row r="54" spans="2:11" ht="17" thickBot="1">
-      <c r="B54" s="79" t="s">
+      <c r="B54" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="69">
+      <c r="C54" s="67">
         <v>0.02</v>
       </c>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="77"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="40"/>
+      <c r="G54" s="51"/>
+      <c r="H54" s="63"/>
       <c r="K54" s="7"/>
     </row>
     <row r="55" spans="2:11" ht="17" thickBot="1">
-      <c r="B55" s="83" t="s">
+      <c r="B55" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="C55" s="71">
+      <c r="C55" s="69">
         <f>C50*(1+C42-C54)^C53</f>
         <v>464397.5305333368</v>
       </c>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40" t="s">
+      <c r="F55" t="s">
         <v>60</v>
       </c>
-      <c r="G55" s="77" t="s">
+      <c r="G55" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="H55" s="81"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="40"/>
+      <c r="H55" s="63"/>
       <c r="K55" s="7"/>
     </row>
     <row r="56" spans="2:11" ht="17" thickBot="1">
@@ -2543,10 +2468,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D4">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="overvalued">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="overvalued">
       <formula>NOT(ISERROR(SEARCH("overvalued",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="undervalued">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="undervalued">
       <formula>NOT(ISERROR(SEARCH("undervalued",D4)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2562,8 +2487,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BA679E-2B2A-8D42-BA3A-7EC56A7FAA94}">
-  <dimension ref="A1:P31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C48EF1BB-6138-2F42-BABE-9DA1934CBC18}">
+  <dimension ref="A1:P56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -2573,8 +2498,8 @@
   <sheetData>
     <row r="1" spans="1:16" ht="17" thickBot="1"/>
     <row r="2" spans="1:16" ht="17" thickBot="1">
-      <c r="B2" s="48" t="s">
-        <v>32</v>
+      <c r="B2" s="47" t="s">
+        <v>61</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
@@ -2593,33 +2518,22 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="7"/>
-      <c r="B3" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="42">
-        <v>100</v>
+      <c r="B3" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="41">
+        <v>32500</v>
       </c>
       <c r="D3" s="39"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
       <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="7"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="43">
-        <v>150</v>
+      <c r="C4" s="42">
+        <v>60</v>
       </c>
       <c r="D4" s="6"/>
       <c r="I4" s="38"/>
@@ -2627,10 +2541,10 @@
     </row>
     <row r="5" spans="1:16" ht="17" customHeight="1" thickBot="1">
       <c r="A5" s="7"/>
-      <c r="B5" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="49">
+      <c r="B5" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="48">
         <v>0</v>
       </c>
       <c r="D5" s="30"/>
@@ -2644,13 +2558,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="7"/>
-      <c r="B6" s="40" t="s">
+      <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="40">
         <v>2025</v>
       </c>
       <c r="E6" s="12">
@@ -2693,7 +2607,7 @@
         <v>2034</v>
       </c>
       <c r="O6" s="13">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>3</v>
@@ -2704,54 +2618,54 @@
         <v>4</v>
       </c>
       <c r="C7" s="32">
-        <v>10</v>
+        <v>3462</v>
       </c>
       <c r="D7" s="14">
         <f>C7*(1+$O$6)</f>
-        <v>10.600000000000001</v>
+        <v>3600.48</v>
       </c>
       <c r="E7" s="14">
         <f>D7*(1+$O$6)</f>
-        <v>11.236000000000002</v>
+        <v>3744.4992000000002</v>
       </c>
       <c r="F7" s="14">
         <f>E7*(1+$O$6)</f>
-        <v>11.910160000000003</v>
+        <v>3894.2791680000005</v>
       </c>
       <c r="G7" s="14">
         <f>F7*(1+$O$6)</f>
-        <v>12.624769600000004</v>
+        <v>4050.0503347200006</v>
       </c>
       <c r="H7" s="14">
         <f>G7*(1+$O$6)</f>
-        <v>13.382255776000004</v>
+        <v>4212.0523481088012</v>
       </c>
       <c r="I7" s="14">
         <f>H7*(1+$O$7)</f>
-        <v>14.185191122560006</v>
+        <v>4338.4139185520653</v>
       </c>
       <c r="J7" s="14">
         <f>I7*(1+$O$7)</f>
-        <v>15.036302589913607</v>
+        <v>4468.5663361086272</v>
       </c>
       <c r="K7" s="14">
         <f>J7*(1+$O$7)</f>
-        <v>15.938480745308425</v>
+        <v>4602.623326191886</v>
       </c>
       <c r="L7" s="14">
         <f>K7*(1+$O$7)</f>
-        <v>16.894789590026932</v>
+        <v>4740.7020259776427</v>
       </c>
       <c r="M7" s="14">
         <f>L7*(1+$O$7)</f>
-        <v>17.908476965428548</v>
+        <v>4882.9230867569722</v>
       </c>
       <c r="N7" s="14">
         <f>L7*O9</f>
-        <v>253.42184385040397</v>
+        <v>71110.530389664636</v>
       </c>
       <c r="O7" s="13">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="P7" s="15" t="s">
         <v>5</v>
@@ -2764,48 +2678,48 @@
         <v>PV(10%)</v>
       </c>
       <c r="D8" s="14">
-        <f>D7*(1+$O$8)^($D$6-D6-1)*$C$5</f>
+        <f t="shared" ref="D8:M8" si="1">D7*(1+$O$8)^($D$6-D6-1)*$C$5</f>
         <v>0</v>
       </c>
       <c r="E8" s="14">
-        <f>E7*(1+$O$8)^($D$6-E6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F8" s="14">
-        <f>F7*(1+$O$8)^($D$6-F6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G8" s="14">
-        <f>G7*(1+$O$8)^($D$6-G6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H8" s="14">
-        <f>H7*(1+$O$8)^($D$6-H6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f>I7*(1+$O$8)^($D$6-I6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="14">
-        <f>J7*(1+$O$8)^($D$6-J6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K8" s="14">
-        <f>K7*(1+$O$8)^($D$6-K6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L8" s="14">
-        <f>L7*(1+$O$8)^($D$6-L6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M8" s="14">
-        <f>M7*(1+$O$8)^($D$6-M6-1)*$C$5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N8" s="14">
         <f>N7*(1+$O$8)^($D$6-N6-1)</f>
-        <v>97.705091291381834</v>
+        <v>27416.187799509968</v>
       </c>
       <c r="O8" s="13">
         <v>0.1</v>
@@ -2821,7 +2735,7 @@
       </c>
       <c r="D9" s="18">
         <f>SUM(D8:N8)</f>
-        <v>97.705091291381834</v>
+        <v>27416.187799509968</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
@@ -2867,39 +2781,39 @@
         <v>2025</v>
       </c>
       <c r="E12" s="12">
-        <f t="shared" ref="E12:M12" si="1">D12+1</f>
+        <f t="shared" ref="E12:M12" si="2">D12+1</f>
         <v>2026</v>
       </c>
       <c r="F12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2027</v>
       </c>
       <c r="G12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2028</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2029</v>
       </c>
       <c r="I12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2030</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2031</v>
       </c>
       <c r="K12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2032</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2033</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2034</v>
       </c>
       <c r="N12" s="12">
@@ -2907,7 +2821,7 @@
         <v>2034</v>
       </c>
       <c r="O12" s="13">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>3</v>
@@ -2919,54 +2833,54 @@
       </c>
       <c r="C13" s="32">
         <f>C7</f>
-        <v>10</v>
+        <v>3462</v>
       </c>
       <c r="D13" s="14">
         <f>C13*(1+$O$12)</f>
-        <v>10.8</v>
+        <v>3635.1000000000004</v>
       </c>
       <c r="E13" s="14">
         <f>D13*(1+$O$12)</f>
-        <v>11.664000000000001</v>
+        <v>3816.8550000000005</v>
       </c>
       <c r="F13" s="14">
         <f>E13*(1+$O$12)</f>
-        <v>12.597120000000002</v>
+        <v>4007.6977500000007</v>
       </c>
       <c r="G13" s="14">
         <f>F13*(1+$O$12)</f>
-        <v>13.604889600000003</v>
+        <v>4208.0826375000006</v>
       </c>
       <c r="H13" s="14">
         <f>G13*(1+$O$12)</f>
-        <v>14.693280768000005</v>
+        <v>4418.4867693750011</v>
       </c>
       <c r="I13" s="14">
         <f>H13*(1+$O$13)</f>
-        <v>15.868743229440007</v>
+        <v>4639.4111078437518</v>
       </c>
       <c r="J13" s="14">
         <f>I13*(1+$O$13)</f>
-        <v>17.138242687795209</v>
+        <v>4871.3816632359394</v>
       </c>
       <c r="K13" s="14">
         <f>J13*(1+$O$13)</f>
-        <v>18.509302102818829</v>
+        <v>5114.950746397737</v>
       </c>
       <c r="L13" s="14">
         <f>K13*(1+$O$13)</f>
-        <v>19.990046271044335</v>
+        <v>5370.6982837176238</v>
       </c>
       <c r="M13" s="14">
         <f>L13*(1+$O$13)</f>
-        <v>21.589249972727885</v>
+        <v>5639.2331979035052</v>
       </c>
       <c r="N13" s="14">
         <f>L13*O15</f>
-        <v>499.75115677610836</v>
+        <v>107413.96567435248</v>
       </c>
       <c r="O13" s="13">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="P13" s="15" t="s">
         <v>5</v>
@@ -2981,48 +2895,48 @@
         <v>PV(10%)</v>
       </c>
       <c r="D14" s="14">
-        <f>D13*(1+$O$14)^($D$12-D12-1)*$C$5</f>
+        <f t="shared" ref="D14:M14" si="3">D13*(1+$O$14)^($D$12-D12-1)*$C$5</f>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f>E13*(1+$O$14)^($D$12-E12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f>F13*(1+$O$14)^($D$12-F12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f>G13*(1+$O$14)^($D$12-G12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f>H13*(1+$O$14)^($D$12-H12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f>I13*(1+$O$14)^($D$12-I12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f>J13*(1+$O$14)^($D$12-J12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f>K13*(1+$O$14)^($D$12-K12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L14" s="14">
-        <f>L13*(1+$O$14)^($D$12-L12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M14" s="14">
-        <f>M13*(1+$O$14)^($D$12-M12-1)*$C$5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14" s="14">
         <f>N13*(1+$O$8)^($D$6-N12-1)</f>
-        <v>192.6757048796743</v>
+        <v>41412.73365676064</v>
       </c>
       <c r="O14" s="13">
         <f>O8</f>
@@ -3039,7 +2953,7 @@
       </c>
       <c r="D15" s="18">
         <f>SUM(D14:N14)</f>
-        <v>192.6757048796743</v>
+        <v>41412.73365676064</v>
       </c>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
@@ -3052,7 +2966,7 @@
       <c r="M15" s="19"/>
       <c r="N15" s="19"/>
       <c r="O15" s="34">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P15" s="7" t="s">
         <v>8</v>
@@ -3085,39 +2999,39 @@
         <v>2025</v>
       </c>
       <c r="E18" s="12">
-        <f t="shared" ref="E18:M18" si="2">D18+1</f>
+        <f t="shared" ref="E18:M18" si="4">D18+1</f>
         <v>2026</v>
       </c>
       <c r="F18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2027</v>
       </c>
       <c r="G18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2028</v>
       </c>
       <c r="H18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2029</v>
       </c>
       <c r="I18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2030</v>
       </c>
       <c r="J18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2031</v>
       </c>
       <c r="K18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2032</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2033</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2034</v>
       </c>
       <c r="N18" s="12">
@@ -3125,7 +3039,7 @@
         <v>2034</v>
       </c>
       <c r="O18" s="13">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="P18" s="7" t="s">
         <v>3</v>
@@ -3137,54 +3051,54 @@
       </c>
       <c r="C19" s="32">
         <f>C13</f>
-        <v>10</v>
+        <v>3462</v>
       </c>
       <c r="D19" s="14">
         <f>C19*(1+$O$18)</f>
-        <v>10.5</v>
+        <v>3565.86</v>
       </c>
       <c r="E19" s="14">
         <f>D19*(1+$O$18)</f>
-        <v>11.025</v>
+        <v>3672.8358000000003</v>
       </c>
       <c r="F19" s="14">
         <f>E19*(1+$O$18)</f>
-        <v>11.576250000000002</v>
+        <v>3783.0208740000003</v>
       </c>
       <c r="G19" s="14">
         <f>F19*(1+$O$18)</f>
-        <v>12.155062500000001</v>
+        <v>3896.5115002200005</v>
       </c>
       <c r="H19" s="14">
         <f>G19*(1+$O$18)</f>
-        <v>12.762815625000002</v>
+        <v>4013.4068452266006</v>
       </c>
       <c r="I19" s="14">
         <f>H19*(1+$O$19)</f>
-        <v>13.400956406250003</v>
+        <v>4133.8090505833989</v>
       </c>
       <c r="J19" s="14">
         <f>I19*(1+$O$19)</f>
-        <v>14.071004226562504</v>
+        <v>4257.8233221009014</v>
       </c>
       <c r="K19" s="14">
         <f>J19*(1+$O$19)</f>
-        <v>14.774554437890631</v>
+        <v>4385.5580217639281</v>
       </c>
       <c r="L19" s="14">
         <f>K19*(1+$O$19)</f>
-        <v>15.513282159785163</v>
+        <v>4517.1247624168464</v>
       </c>
       <c r="M19" s="14">
         <f>L19*(1+$O$19)</f>
-        <v>16.288946267774421</v>
+        <v>4652.638505289352</v>
       </c>
       <c r="N19" s="14">
         <f>L19*O21</f>
-        <v>186.15938591742196</v>
+        <v>45171.247624168464</v>
       </c>
       <c r="O19" s="13">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="P19" s="15" t="s">
         <v>5</v>
@@ -3199,48 +3113,48 @@
         <v>PV(10%)</v>
       </c>
       <c r="D20" s="14">
-        <f>D19*(1+$O$20)^($D$18-D18-1)*$C$5</f>
+        <f t="shared" ref="D20:M20" si="5">D19*(1+$O$20)^($D$18-D18-1)*$C$5</f>
         <v>0</v>
       </c>
       <c r="E20" s="14">
-        <f>E19*(1+$O$20)^($D$18-E18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <f>F19*(1+$O$20)^($D$18-F18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G20" s="14">
-        <f>G19*(1+$O$20)^($D$18-G18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H20" s="14">
-        <f>H19*(1+$O$20)^($D$18-H18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f>I19*(1+$O$20)^($D$18-I18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J20" s="14">
-        <f>J19*(1+$O$20)^($D$18-J18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K20" s="14">
-        <f>K19*(1+$O$20)^($D$18-K18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L20" s="14">
-        <f>L19*(1+$O$20)^($D$18-L18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M20" s="14">
-        <f>M19*(1+$O$20)^($D$18-M18-1)*$C$5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N20" s="14">
-        <f t="shared" ref="N20" si="3">N19*(1+$O$20)^($D$18-N18-1)</f>
-        <v>71.772502004784457</v>
+        <f t="shared" ref="N20" si="6">N19*(1+$O$20)^($D$18-N18-1)</f>
+        <v>17415.471396657817</v>
       </c>
       <c r="O20" s="13">
         <f>O14</f>
@@ -3257,7 +3171,7 @@
       </c>
       <c r="D21" s="18">
         <f>SUM(D20:N20)</f>
-        <v>71.772502004784457</v>
+        <v>17415.471396657817</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="19"/>
@@ -3270,7 +3184,7 @@
       <c r="M21" s="19"/>
       <c r="N21" s="19"/>
       <c r="O21" s="34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P21" s="7" t="s">
         <v>8</v>
@@ -3309,11 +3223,11 @@
       </c>
       <c r="E24" s="14">
         <f>D9</f>
-        <v>97.705091291381834</v>
+        <v>27416.187799509968</v>
       </c>
       <c r="F24" s="23">
         <f>E24*D24</f>
-        <v>32.24268012615601</v>
+        <v>9047.3419738382891</v>
       </c>
       <c r="I24" t="s">
         <v>26</v>
@@ -3330,11 +3244,11 @@
       </c>
       <c r="E25" s="14">
         <f>D15</f>
-        <v>192.6757048796743</v>
+        <v>41412.73365676064</v>
       </c>
       <c r="F25" s="23">
         <f>E25*D25</f>
-        <v>65.509739659089263</v>
+        <v>14080.329443298619</v>
       </c>
       <c r="I25" s="37" t="s">
         <v>27</v>
@@ -3346,34 +3260,34 @@
       <c r="C26" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="50">
         <v>0.33</v>
       </c>
       <c r="E26" s="25">
         <f>D21</f>
-        <v>71.772502004784457</v>
+        <v>17415.471396657817</v>
       </c>
       <c r="F26" s="26">
         <f>E26*D26</f>
-        <v>23.684925661578873</v>
+        <v>5747.1055608970801</v>
       </c>
       <c r="P26" s="7"/>
     </row>
     <row r="27" spans="2:16" ht="17" thickBot="1">
       <c r="B27" s="10"/>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="5">
         <f>C3</f>
-        <v>100</v>
+        <v>32500</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>21</v>
       </c>
       <c r="F27" s="28">
         <f>SUM(F24:F26)</f>
-        <v>121.43734544682415</v>
+        <v>28874.776978033988</v>
       </c>
       <c r="P27" s="7"/>
     </row>
@@ -3408,6 +3322,244 @@
       <c r="O31" s="30"/>
       <c r="P31" s="31"/>
     </row>
+    <row r="36" spans="2:11" ht="17" thickBot="1"/>
+    <row r="37" spans="2:11" ht="17" thickBot="1">
+      <c r="B37" s="70"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="72" t="s">
+        <v>37</v>
+      </c>
+      <c r="H37" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="4"/>
+    </row>
+    <row r="38" spans="2:11" ht="17" thickBot="1">
+      <c r="B38" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="54">
+        <v>32500</v>
+      </c>
+      <c r="G38" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="56">
+        <v>0.12</v>
+      </c>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39" s="74"/>
+      <c r="C39" s="51"/>
+      <c r="G39" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="H39" s="56">
+        <v>0.09</v>
+      </c>
+      <c r="K39" s="7"/>
+    </row>
+    <row r="40" spans="2:11">
+      <c r="B40" s="75" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="51"/>
+      <c r="G40" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" s="56">
+        <v>0.08</v>
+      </c>
+      <c r="K40" s="7"/>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="H41" s="56">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K41" s="7"/>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="B42" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="59">
+        <f>VLOOKUP(C41,G38:H43,2)</f>
+        <v>0.08</v>
+      </c>
+      <c r="D42" s="60"/>
+      <c r="G42" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" s="56">
+        <v>0.06</v>
+      </c>
+      <c r="K42" s="7"/>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="B43" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="61">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G43" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="H43" s="62">
+        <v>0.1</v>
+      </c>
+      <c r="K43" s="7"/>
+    </row>
+    <row r="44" spans="2:11">
+      <c r="B44" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="61">
+        <v>0.04</v>
+      </c>
+      <c r="G44" s="51"/>
+      <c r="H44" s="63"/>
+      <c r="K44" s="7"/>
+    </row>
+    <row r="45" spans="2:11">
+      <c r="B45" s="74"/>
+      <c r="C45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="63"/>
+      <c r="K45" s="7"/>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="B46" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="63"/>
+      <c r="K46" s="7"/>
+    </row>
+    <row r="47" spans="2:11">
+      <c r="B47" s="76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="61">
+        <v>0.16</v>
+      </c>
+      <c r="G47" s="51"/>
+      <c r="H47" s="63"/>
+      <c r="K47" s="7"/>
+    </row>
+    <row r="48" spans="2:11">
+      <c r="B48" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="61">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="G48" s="51"/>
+      <c r="H48" s="63"/>
+      <c r="K48" s="7"/>
+    </row>
+    <row r="49" spans="2:11" ht="17" thickBot="1">
+      <c r="B49" s="74"/>
+      <c r="C49" s="51"/>
+      <c r="G49" s="51"/>
+      <c r="H49" s="63"/>
+      <c r="K49" s="7"/>
+    </row>
+    <row r="50" spans="2:11" ht="17" thickBot="1">
+      <c r="B50" s="74" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="64">
+        <f>C38/(C47*(1+C44)*(1-C44/C48)/(C42-C44))</f>
+        <v>13939.950980392154</v>
+      </c>
+      <c r="G50" s="51"/>
+      <c r="H50" s="63"/>
+      <c r="K50" s="7"/>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="74"/>
+      <c r="C51" s="65"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="63"/>
+      <c r="K51" s="7"/>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52" s="74" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="65"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="63"/>
+      <c r="K52" s="7"/>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="66">
+        <v>5</v>
+      </c>
+      <c r="G53" s="51"/>
+      <c r="H53" s="63"/>
+      <c r="K53" s="7"/>
+    </row>
+    <row r="54" spans="2:11" ht="17" thickBot="1">
+      <c r="B54" s="76" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="67">
+        <v>0.02</v>
+      </c>
+      <c r="G54" s="51"/>
+      <c r="H54" s="63"/>
+      <c r="K54" s="7"/>
+    </row>
+    <row r="55" spans="2:11" ht="17" thickBot="1">
+      <c r="B55" s="77" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="69">
+        <f>C50*(1+C42-C54)^C53</f>
+        <v>18654.798952450983</v>
+      </c>
+      <c r="F55" t="s">
+        <v>60</v>
+      </c>
+      <c r="G55" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="H55" s="63"/>
+      <c r="K55" s="7"/>
+    </row>
+    <row r="56" spans="2:11" ht="17" thickBot="1">
+      <c r="B56" s="24"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="31"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="D4">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="overvalued">
@@ -3417,12 +3569,867 @@
       <formula>NOT(ISERROR(SEARCH("undervalued",D4)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C41" xr:uid="{8E66BC7E-C841-004A-8C72-E154D31D17DB}">
+      <formula1>$F$2:$F$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BA679E-2B2A-8D42-BA3A-7EC56A7FAA94}">
+  <dimension ref="A1:P31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="16" max="16" width="23.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="17" thickBot="1"/>
+    <row r="2" spans="1:16" ht="17" thickBot="1">
+      <c r="B2" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="4"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="7"/>
+      <c r="B3" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="41">
+        <v>100</v>
+      </c>
+      <c r="D3" s="39"/>
+      <c r="P3" s="7"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="7"/>
+      <c r="B4" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="42">
+        <v>150</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="I4" s="38"/>
+      <c r="P4" s="7"/>
+    </row>
+    <row r="5" spans="1:16" ht="17" customHeight="1" thickBot="1">
+      <c r="A5" s="7"/>
+      <c r="B5" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="48">
+        <v>0</v>
+      </c>
+      <c r="D5" s="30"/>
+      <c r="N5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="7"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="7"/>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="40">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="12">
+        <f t="shared" ref="E6:M6" si="0">D6+1</f>
+        <v>2026</v>
+      </c>
+      <c r="F6" s="12">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+      <c r="G6" s="12">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="H6" s="12">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="0"/>
+        <v>2031</v>
+      </c>
+      <c r="K6" s="12">
+        <f t="shared" si="0"/>
+        <v>2032</v>
+      </c>
+      <c r="L6" s="12">
+        <f t="shared" si="0"/>
+        <v>2033</v>
+      </c>
+      <c r="M6" s="12">
+        <f t="shared" si="0"/>
+        <v>2034</v>
+      </c>
+      <c r="N6" s="12">
+        <v>2034</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="32">
+        <v>10</v>
+      </c>
+      <c r="D7" s="14">
+        <f>C7*(1+$O$6)</f>
+        <v>10.600000000000001</v>
+      </c>
+      <c r="E7" s="14">
+        <f>D7*(1+$O$6)</f>
+        <v>11.236000000000002</v>
+      </c>
+      <c r="F7" s="14">
+        <f>E7*(1+$O$6)</f>
+        <v>11.910160000000003</v>
+      </c>
+      <c r="G7" s="14">
+        <f>F7*(1+$O$6)</f>
+        <v>12.624769600000004</v>
+      </c>
+      <c r="H7" s="14">
+        <f>G7*(1+$O$6)</f>
+        <v>13.382255776000004</v>
+      </c>
+      <c r="I7" s="14">
+        <f>H7*(1+$O$7)</f>
+        <v>14.185191122560006</v>
+      </c>
+      <c r="J7" s="14">
+        <f>I7*(1+$O$7)</f>
+        <v>15.036302589913607</v>
+      </c>
+      <c r="K7" s="14">
+        <f>J7*(1+$O$7)</f>
+        <v>15.938480745308425</v>
+      </c>
+      <c r="L7" s="14">
+        <f>K7*(1+$O$7)</f>
+        <v>16.894789590026932</v>
+      </c>
+      <c r="M7" s="14">
+        <f>L7*(1+$O$7)</f>
+        <v>17.908476965428548</v>
+      </c>
+      <c r="N7" s="14">
+        <f>L7*O9</f>
+        <v>253.42184385040397</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8" s="10"/>
+      <c r="C8" s="16" t="str">
+        <f>CONCATENATE("PV(",O8*100,"%)")</f>
+        <v>PV(10%)</v>
+      </c>
+      <c r="D8" s="14">
+        <f t="shared" ref="D8:M8" si="1">D7*(1+$O$8)^($D$6-D6-1)*$C$5</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="14">
+        <f>N7*(1+$O$8)^($D$6-N6-1)</f>
+        <v>97.705091291381834</v>
+      </c>
+      <c r="O8" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="17" thickBot="1">
+      <c r="B9" s="10"/>
+      <c r="C9" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="18">
+        <f>SUM(D8:N8)</f>
+        <v>97.705091291381834</v>
+      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="34">
+        <v>15</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="B10" s="10"/>
+      <c r="P10" s="7"/>
+    </row>
+    <row r="11" spans="1:16" ht="30" thickBot="1">
+      <c r="B11" s="10"/>
+      <c r="N11" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="7"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="B12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="11" t="str">
+        <f>C6</f>
+        <v>Owner's Earning</v>
+      </c>
+      <c r="D12" s="12">
+        <f>D6</f>
+        <v>2025</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12:M12" si="2">D12+1</f>
+        <v>2026</v>
+      </c>
+      <c r="F12" s="12">
+        <f t="shared" si="2"/>
+        <v>2027</v>
+      </c>
+      <c r="G12" s="12">
+        <f t="shared" si="2"/>
+        <v>2028</v>
+      </c>
+      <c r="H12" s="12">
+        <f t="shared" si="2"/>
+        <v>2029</v>
+      </c>
+      <c r="I12" s="12">
+        <f t="shared" si="2"/>
+        <v>2030</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" si="2"/>
+        <v>2031</v>
+      </c>
+      <c r="K12" s="12">
+        <f t="shared" si="2"/>
+        <v>2032</v>
+      </c>
+      <c r="L12" s="12">
+        <f t="shared" si="2"/>
+        <v>2033</v>
+      </c>
+      <c r="M12" s="12">
+        <f t="shared" si="2"/>
+        <v>2034</v>
+      </c>
+      <c r="N12" s="12">
+        <f>N6</f>
+        <v>2034</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="32">
+        <f>C7</f>
+        <v>10</v>
+      </c>
+      <c r="D13" s="14">
+        <f>C13*(1+$O$12)</f>
+        <v>10.8</v>
+      </c>
+      <c r="E13" s="14">
+        <f>D13*(1+$O$12)</f>
+        <v>11.664000000000001</v>
+      </c>
+      <c r="F13" s="14">
+        <f>E13*(1+$O$12)</f>
+        <v>12.597120000000002</v>
+      </c>
+      <c r="G13" s="14">
+        <f>F13*(1+$O$12)</f>
+        <v>13.604889600000003</v>
+      </c>
+      <c r="H13" s="14">
+        <f>G13*(1+$O$12)</f>
+        <v>14.693280768000005</v>
+      </c>
+      <c r="I13" s="14">
+        <f>H13*(1+$O$13)</f>
+        <v>15.868743229440007</v>
+      </c>
+      <c r="J13" s="14">
+        <f>I13*(1+$O$13)</f>
+        <v>17.138242687795209</v>
+      </c>
+      <c r="K13" s="14">
+        <f>J13*(1+$O$13)</f>
+        <v>18.509302102818829</v>
+      </c>
+      <c r="L13" s="14">
+        <f>K13*(1+$O$13)</f>
+        <v>19.990046271044335</v>
+      </c>
+      <c r="M13" s="14">
+        <f>L13*(1+$O$13)</f>
+        <v>21.589249972727885</v>
+      </c>
+      <c r="N13" s="14">
+        <f>L13*O15</f>
+        <v>499.75115677610836</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="B14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="16" t="str">
+        <f>CONCATENATE("PV(",O14*100,"%)")</f>
+        <v>PV(10%)</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" ref="D14:M14" si="3">D13*(1+$O$14)^($D$12-D12-1)*$C$5</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="14">
+        <f>N13*(1+$O$8)^($D$6-N12-1)</f>
+        <v>192.6757048796743</v>
+      </c>
+      <c r="O14" s="13">
+        <f>O8</f>
+        <v>0.1</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="17" thickBot="1">
+      <c r="B15" s="10"/>
+      <c r="C15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="18">
+        <f>SUM(D14:N14)</f>
+        <v>192.6757048796743</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="34">
+        <v>25</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16" s="10"/>
+      <c r="P16" s="7"/>
+    </row>
+    <row r="17" spans="2:16" ht="30" thickBot="1">
+      <c r="B17" s="10"/>
+      <c r="N17" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P17" s="7"/>
+    </row>
+    <row r="18" spans="2:16">
+      <c r="B18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="11" t="str">
+        <f>C12</f>
+        <v>Owner's Earning</v>
+      </c>
+      <c r="D18" s="12">
+        <f>D12</f>
+        <v>2025</v>
+      </c>
+      <c r="E18" s="12">
+        <f t="shared" ref="E18:M18" si="4">D18+1</f>
+        <v>2026</v>
+      </c>
+      <c r="F18" s="12">
+        <f t="shared" si="4"/>
+        <v>2027</v>
+      </c>
+      <c r="G18" s="12">
+        <f t="shared" si="4"/>
+        <v>2028</v>
+      </c>
+      <c r="H18" s="12">
+        <f t="shared" si="4"/>
+        <v>2029</v>
+      </c>
+      <c r="I18" s="12">
+        <f t="shared" si="4"/>
+        <v>2030</v>
+      </c>
+      <c r="J18" s="12">
+        <f t="shared" si="4"/>
+        <v>2031</v>
+      </c>
+      <c r="K18" s="12">
+        <f t="shared" si="4"/>
+        <v>2032</v>
+      </c>
+      <c r="L18" s="12">
+        <f t="shared" si="4"/>
+        <v>2033</v>
+      </c>
+      <c r="M18" s="12">
+        <f t="shared" si="4"/>
+        <v>2034</v>
+      </c>
+      <c r="N18" s="12">
+        <f>N12</f>
+        <v>2034</v>
+      </c>
+      <c r="O18" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16">
+      <c r="B19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="32">
+        <f>C13</f>
+        <v>10</v>
+      </c>
+      <c r="D19" s="14">
+        <f>C19*(1+$O$18)</f>
+        <v>10.5</v>
+      </c>
+      <c r="E19" s="14">
+        <f>D19*(1+$O$18)</f>
+        <v>11.025</v>
+      </c>
+      <c r="F19" s="14">
+        <f>E19*(1+$O$18)</f>
+        <v>11.576250000000002</v>
+      </c>
+      <c r="G19" s="14">
+        <f>F19*(1+$O$18)</f>
+        <v>12.155062500000001</v>
+      </c>
+      <c r="H19" s="14">
+        <f>G19*(1+$O$18)</f>
+        <v>12.762815625000002</v>
+      </c>
+      <c r="I19" s="14">
+        <f>H19*(1+$O$19)</f>
+        <v>13.400956406250003</v>
+      </c>
+      <c r="J19" s="14">
+        <f>I19*(1+$O$19)</f>
+        <v>14.071004226562504</v>
+      </c>
+      <c r="K19" s="14">
+        <f>J19*(1+$O$19)</f>
+        <v>14.774554437890631</v>
+      </c>
+      <c r="L19" s="14">
+        <f>K19*(1+$O$19)</f>
+        <v>15.513282159785163</v>
+      </c>
+      <c r="M19" s="14">
+        <f>L19*(1+$O$19)</f>
+        <v>16.288946267774421</v>
+      </c>
+      <c r="N19" s="14">
+        <f>L19*O21</f>
+        <v>186.15938591742196</v>
+      </c>
+      <c r="O19" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="P19" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16">
+      <c r="B20" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="16" t="str">
+        <f>CONCATENATE("PV(",O20*100,"%)")</f>
+        <v>PV(10%)</v>
+      </c>
+      <c r="D20" s="14">
+        <f t="shared" ref="D20:M20" si="5">D19*(1+$O$20)^($D$18-D18-1)*$C$5</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="14">
+        <f t="shared" ref="N20" si="6">N19*(1+$O$20)^($D$18-N18-1)</f>
+        <v>71.772502004784457</v>
+      </c>
+      <c r="O20" s="13">
+        <f>O14</f>
+        <v>0.1</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" ht="17" thickBot="1">
+      <c r="B21" s="10"/>
+      <c r="C21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="18">
+        <f>SUM(D20:N20)</f>
+        <v>71.772502004784457</v>
+      </c>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="34">
+        <v>12</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="17" thickBot="1">
+      <c r="B22" s="10"/>
+      <c r="P22" s="7"/>
+    </row>
+    <row r="23" spans="2:16" ht="17" thickBot="1">
+      <c r="B23" s="10"/>
+      <c r="C23" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" s="7"/>
+    </row>
+    <row r="24" spans="2:16">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="36">
+        <v>0.33</v>
+      </c>
+      <c r="E24" s="14">
+        <f>D9</f>
+        <v>97.705091291381834</v>
+      </c>
+      <c r="F24" s="23">
+        <f>E24*D24</f>
+        <v>32.24268012615601</v>
+      </c>
+      <c r="I24" t="s">
+        <v>26</v>
+      </c>
+      <c r="P24" s="7"/>
+    </row>
+    <row r="25" spans="2:16">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="36">
+        <v>0.34</v>
+      </c>
+      <c r="E25" s="14">
+        <f>D15</f>
+        <v>192.6757048796743</v>
+      </c>
+      <c r="F25" s="23">
+        <f>E25*D25</f>
+        <v>65.509739659089263</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="P25" s="7"/>
+    </row>
+    <row r="26" spans="2:16" ht="17" thickBot="1">
+      <c r="B26" s="10"/>
+      <c r="C26" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="50">
+        <v>0.33</v>
+      </c>
+      <c r="E26" s="25">
+        <f>D21</f>
+        <v>71.772502004784457</v>
+      </c>
+      <c r="F26" s="26">
+        <f>E26*D26</f>
+        <v>23.684925661578873</v>
+      </c>
+      <c r="P26" s="7"/>
+    </row>
+    <row r="27" spans="2:16" ht="17" thickBot="1">
+      <c r="B27" s="10"/>
+      <c r="C27" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="49">
+        <f>C3</f>
+        <v>100</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="28">
+        <f>SUM(F24:F26)</f>
+        <v>121.43734544682415</v>
+      </c>
+      <c r="P27" s="7"/>
+    </row>
+    <row r="28" spans="2:16">
+      <c r="B28" s="10"/>
+      <c r="P28" s="7"/>
+    </row>
+    <row r="29" spans="2:16">
+      <c r="B29" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" s="7"/>
+    </row>
+    <row r="30" spans="2:16">
+      <c r="B30" s="10"/>
+      <c r="P30" s="7"/>
+    </row>
+    <row r="31" spans="2:16" ht="17" thickBot="1">
+      <c r="B31" s="24"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="31"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="overvalued">
+      <formula>NOT(ISERROR(SEARCH("overvalued",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="undervalued">
+      <formula>NOT(ISERROR(SEARCH("undervalued",D4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD1D9DB-4203-854E-AE74-4284527EA313}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -3434,205 +4441,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17" thickBot="1">
-      <c r="A1" s="53"/>
-      <c r="B1" s="53"/>
-      <c r="F1" s="54" t="s">
+      <c r="A1" s="51"/>
+      <c r="B1" s="51"/>
+      <c r="F1" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="G1" s="53" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" thickBot="1">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="56">
+      <c r="B2" s="54">
         <v>1047150</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2" s="56">
         <v>0.12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="F3" s="57" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="F3" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="58">
+      <c r="G3" s="56">
         <v>0.09</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="F4" s="57" t="s">
+      <c r="B4" s="51"/>
+      <c r="F4" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="56">
         <v>0.08</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="56">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="61">
+      <c r="B6" s="59">
         <f>VLOOKUP(B5,F2:G7,2)</f>
         <v>0.08</v>
       </c>
-      <c r="C6" s="62"/>
-      <c r="F6" s="57" t="s">
+      <c r="C6" s="60"/>
+      <c r="F6" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="56">
         <v>0.06</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="63">
+      <c r="B7" s="61">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F7" s="57" t="s">
+      <c r="F7" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="64">
+      <c r="G7" s="62">
         <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="63">
+      <c r="B8" s="61">
         <v>0.04</v>
       </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="65"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="63"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="53"/>
-      <c r="B9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="65"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="63"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="65"/>
+      <c r="B10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="63"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="63">
+      <c r="B11" s="61">
         <v>0.182</v>
       </c>
-      <c r="F11" s="53"/>
-      <c r="G11" s="65"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="63"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="63">
+      <c r="B12" s="61">
         <v>0.1104</v>
       </c>
-      <c r="F12" s="53"/>
-      <c r="G12" s="65"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="63"/>
     </row>
     <row r="13" spans="1:7" ht="17" thickBot="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="65"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="63"/>
     </row>
     <row r="14" spans="1:7" ht="17" thickBot="1">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="66">
+      <c r="B14" s="64">
         <f>B2/(B11*(1+B8)*(1-B8/B12)/(B6-B8))</f>
         <v>347024.85014985013</v>
       </c>
-      <c r="F14" s="53"/>
-      <c r="G14" s="65"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="63"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="53"/>
-      <c r="B15" s="67"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="65"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="65"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="63"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="65"/>
+      <c r="B16" s="65"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="63"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="68">
+      <c r="B17" s="66">
         <v>5</v>
       </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="65"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="63"/>
     </row>
     <row r="18" spans="1:7" ht="17" thickBot="1">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="69">
+      <c r="B18" s="67">
         <v>0.02</v>
       </c>
-      <c r="F18" s="53"/>
-      <c r="G18" s="65"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="63"/>
     </row>
     <row r="19" spans="1:7" ht="17" thickBot="1">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="71">
+      <c r="B19" s="69">
         <f>B14*(1+B6-B18)^B17</f>
         <v>464397.5305333368</v>
       </c>
       <c r="E19" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="53" t="s">
+      <c r="F19" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="65"/>
+      <c r="G19" s="63"/>
     </row>
   </sheetData>
   <dataValidations count="1">
